--- a/docs/药液配置加注控制系统_BOM清单_v2.xlsx
+++ b/docs/药液配置加注控制系统_BOM清单_v2.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="348" yWindow="1104" windowWidth="13668" windowHeight="11256" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BOM清单" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'BOM清单'!$A$1:$G$29</definedName>
@@ -609,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" style="13" min="1" max="1"/>
@@ -623,14 +623,14 @@
     <row r="1" ht="25.95" customHeight="1" s="13">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>药液配置与加注控制系统 — BOM（v2，按8套独立控制单元核算）</t>
+          <t>药液配置与加注控制系统 — BOM（v2，按8套独立控制单元核算，同步至PLC设计文档v9.2）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="13">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>依据《药液配置加注控制系统_PLC设计文档》v9版整理，8套缸独立控制单元架构；部分条目规格/型号及控制柜布置方案待现场确认，详见备注列</t>
+          <t>依据《药液配置加注控制系统_PLC设计文档》v9.2版整理，8套缸独立控制单元架构；v9.2取消温度计、pH计两个485从站；部分条目规格/型号及控制柜布置方案待现场确认，详见备注列</t>
         </is>
       </c>
     </row>
@@ -740,12 +740,12 @@
       <c r="B7" s="10" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>中控室SCADA上位机</t>
+          <t>本地集中触摸屏HMI</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>工控机/PC+显示器，用于集中监控8套缸单元运行状态、参数设定、历史数据查看</t>
+          <t>工业触摸屏，10~15寸（建议12寸以上），支持S7-200 SMART以太网通讯（S7协议/Modbus TCP），支持8站点同时连接</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -758,7 +758,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>具体配置待SCADA软件选型确定后核算</t>
+          <t>现场1台集中管理8套缸单元，用于总览/报警详情/报警确认/参数设定/历史记录/手动调试；优先昆仑通态MCGS、威纶通、步科、显控等，需向厂家确认8站点同时通讯能力、变量点数、报警/历史记录容量</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>SCADA组态软件</t>
+          <t>HMI组态软件</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>建议优先选用昆仑通态MCGS工控版（PC版）；需向厂商确认其S7-200 SMART以太网驱动支持方式（S7协议/Modbus TCP）及8站点同时在线授权点数是否满足</t>
+          <t>随屏提供的组态工程软件，或免费版组态软件</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
@@ -787,7 +787,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>选型待定，不满足需改选其他支持S7-200 SMART的第三方SCADA软件</t>
+          <t>优先选用随屏免费提供的组态软件（如昆仑通态MCGS嵌入版）；需确认S7-200 SMART以太网驱动支持方式、8站点授权、变量点数及报警/历史记录容量是否满足</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>9口及以上非网管型，用于连接8台PLC＋1台SCADA上位机</t>
+          <t>9口及以上非网管型，用于连接8台PLC＋1台本地集中HMI</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -1035,7 +1035,7 @@
       <c r="A17" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="n"/>
+      <c r="B17" s="11" t="n"/>
       <c r="C17" s="4" t="inlineStr">
         <is>
           <t>流量计</t>
@@ -1064,28 +1064,32 @@
       <c r="A18" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="10" t="n"/>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>泵类设备</t>
+        </is>
+      </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>温度计</t>
+          <t>潜水泵</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Modbus RTU 485通讯</t>
+          <t>上缸搅拌用，串接流量开关做运行反馈</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，共8个，接口文档待补充</t>
+          <t>每套缸2台，共8套16台</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1100,12 @@
       <c r="B19" s="11" t="n"/>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>pH计</t>
+          <t>注射泵（泵阀一体）</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Modbus RTU 485通讯</t>
+          <t>柱塞式计量泵，Modbus RTU 485通讯，含内部切换阀</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
@@ -1109,12 +1113,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，共8个，接口文档待补充</t>
+          <t>每套缸1台，共8台，已确认Modbus协议，配套进样器规格按加药量核实</t>
         </is>
       </c>
     </row>
@@ -1124,30 +1128,30 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>泵类设备</t>
+          <t>安全与保护装置</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>潜水泵</t>
+          <t>急停按钮</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>上缸搅拌用，串接流量开关做运行反馈</t>
+          <t>工业级，至少2组独立常闭触点（1组接安全继电器，1组接PLC监测）</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>每套缸2台，共8套16台</t>
+          <t>每套缸1个，各自独立，不设总控室级联动急停</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1162,12 @@
       <c r="B21" s="11" t="n"/>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>注射泵（泵阀一体）</t>
+          <t>安全继电器</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>柱塞式计量泵，Modbus RTU 485通讯，含内部切换阀</t>
+          <t>强制导向型（force-guided），建议符合EN ISO 13849-1/IEC 60204-1标准</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
@@ -1171,12 +1175,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>每套缸1台，共8台，已确认Modbus协议，配套进样器规格按加药量核实</t>
+          <t>每套缸1个，切断该套单元潜水泵/注射泵/电动球阀动力回路</t>
         </is>
       </c>
     </row>
@@ -1186,21 +1190,21 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>安全与保护装置</t>
+          <t>电气辅材</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>急停按钮</t>
+          <t>中间继电器（DO输出驱动）</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>工业级，至少2组独立常闭触点（1组接安全继电器，1组接PLC监测）</t>
+          <t>PLC数字量输出统一经继电器转换驱动负载，24V DC线圈</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1209,7 +1213,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，各自独立，不设总控室级联动急停</t>
+          <t>每套缸9个（对应9个DO点：潜水泵×2、电动球阀×3、NC电磁阀×2、声/光报警×2），共8套72个</t>
         </is>
       </c>
     </row>
@@ -1217,19 +1221,19 @@
       <c r="A23" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="n"/>
+      <c r="B23" s="10" t="n"/>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>安全继电器</t>
+          <t>中间继电器（DI有源信号转换）</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>强制导向型（force-guided），建议符合EN ISO 13849-1/IEC 60204-1标准</t>
+          <t>阀门限位反馈为有源正极输出，需转换为无源触点接入PLC</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1238,7 +1242,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，切断该套单元潜水泵/注射泵/电动球阀动力回路</t>
+          <t>每套缸6个（阀A/B/C各自开到位/关到位共6路），共8套48个</t>
         </is>
       </c>
     </row>
@@ -1246,32 +1250,28 @@
       <c r="A24" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>电气辅材</t>
-        </is>
-      </c>
+      <c r="B24" s="10" t="n"/>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>中间继电器（DO输出驱动）</t>
+          <t>导轨、端子排、线槽</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>PLC数字量输出统一经继电器转换驱动负载，24V DC线圈</t>
+          <t>标准DIN导轨安装，含接线端子、线槽、标签</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>批</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>每套缸9个（对应9个DO点：潜水泵×2、电动球阀×3、NC电磁阀×2、声/光报警×2），共8套72个</t>
+          <t>每套缸单元1批，共8批；若控制柜改为集中大柜方案可合并核算用量</t>
         </is>
       </c>
     </row>
@@ -1282,25 +1282,25 @@
       <c r="B25" s="10" t="n"/>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>中间继电器（DI有源信号转换）</t>
+          <t>RS485通讯电缆</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>阀门限位反馈为有源正极输出，需转换为无源触点接入PLC</t>
+          <t>屏蔽双绞线，每套单元1条独立总线，连接本单元PLC与2个485从站（注射泵/流量计）</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>批</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>每套缸6个（阀A/B/C各自开到位/关到位共6路），共8套48个</t>
+          <t>每套缸独立1批总线，共8批，不与其他单元共享总线</t>
         </is>
       </c>
     </row>
@@ -1308,28 +1308,28 @@
       <c r="A26" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="10" t="n"/>
+      <c r="B26" s="11" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>导轨、端子排、线槽</t>
+          <t>RS485终端匹配电阻</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>标准DIN导轨安装，含接线端子、线槽、标签</t>
+          <t>120Ω，每条总线两端各接1个</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>批</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>每套缸单元1批，共8批；若控制柜改为集中大柜方案可合并核算用量</t>
+          <t>每套缸2个，共8套16个</t>
         </is>
       </c>
     </row>
@@ -1337,15 +1337,19 @@
       <c r="A27" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="10" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>报警装置</t>
+        </is>
+      </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>RS485通讯电缆</t>
+          <t>声音报警器</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>屏蔽双绞线，每套单元1条独立总线，连接本单元PLC与4个485从站（注射泵/温度计/pH计/流量计）</t>
+          <t>无源触点驱动，独立消音控制</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1353,12 +1357,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>批</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>每套缸独立1批总线，共8批，不与其他单元共享总线</t>
+          <t>每套缸1个，各自独立，不设总控室汇总报警</t>
         </is>
       </c>
     </row>
@@ -1369,16 +1373,16 @@
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>RS485终端匹配电阻</t>
+          <t>灯光报警器/指示灯</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>120Ω，每条总线两端各接1个</t>
+          <t>无源触点驱动，独立消光控制（需就地面板按钮人工确认复位）</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1387,7 +1391,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>每套缸2个，共8套16个</t>
+          <t>每套缸1个，各自独立</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1401,17 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>报警装置</t>
+          <t>柜体</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>声音报警器</t>
+          <t>控制柜</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>无源触点驱动，独立消音控制</t>
+          <t>含PLC、继电器、端子排等全部电气元件安装空间</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1415,98 +1419,32 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，各自独立，不设总控室汇总报警</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="372" customHeight="1" s="13">
-      <c r="A30" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>灯光报警器/指示灯</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>无源触点驱动，独立消光控制（需就地面板按钮人工确认复位）</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>个</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>每套缸1个，各自独立</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>柜体</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>控制柜</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>含PLC、继电器、端子排等全部电气元件安装空间</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
           <t>布置方案（8套独立小柜就近安装 / 1个大柜内隔8个分区）待现场勘察玻璃缸实际摆放布局后确定；此处暂按独立小柜方案列8台，若改集中大柜需合并调整</t>
         </is>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>说明：本清单为核心控制类元件清单，不含管路、接头、支架等安装辅材；标注"待定/待确认"的条目需完成相应技术文档确认后再定型号；数量按"8套缸独立控制单元"架构核算（每套缸1台PLC、1条485总线），控制柜/电源具体布置待现场勘察后可能调整。</t>
-        </is>
-      </c>
+    <row r="30" ht="372" customHeight="1" s="13"/>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="B27:B28"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B15:B17"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B22:B26"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B15:B19"/>
     <mergeCell ref="B5:B12"/>
-    <mergeCell ref="B29:B30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0"/>

--- a/docs/药液配置加注控制系统_BOM清单_v2.xlsx
+++ b/docs/药液配置加注控制系统_BOM清单_v2.xlsx
@@ -623,14 +623,14 @@
     <row r="1" ht="25.95" customHeight="1" s="13">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>药液配置与加注控制系统 — BOM（v2，按8套独立控制单元核算，同步至PLC设计文档v9.2）</t>
+          <t>药液配置与加注控制系统 — BOM（v2，按8套独立控制单元核算，同步至PLC设计文档v9.3，支持分期接入）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="13">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>依据《药液配置加注控制系统_PLC设计文档》v9.2版整理，8套缸独立控制单元架构；v9.2取消温度计、pH计两个485从站；部分条目规格/型号及控制柜布置方案待现场确认，详见备注列</t>
+          <t>依据《药液配置加注控制系统_PLC设计文档》v9.3版整理，8套缸独立控制单元架构；v9.2取消温度计、pH计两个485从站；v9.3首期先实施1套、后续按需扩展至8套，按套采购条目备注标注"首期1套/全量8套"，公共设备首期即按全量8套规划容量；部分条目规格/型号及控制柜布置方案待现场确认，详见备注列</t>
         </is>
       </c>
     </row>
@@ -690,8 +690,10 @@
           <t>西门子 S7-200 SMART CPU ST20（标准型，内置RTC）</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>8</v>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -700,7 +702,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>每套缸单元1台，共8台，各自独立运行，互不依赖</t>
+          <t>每套缸单元1台，共8台，各自独立运行，互不依赖；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -719,8 +721,10 @@
           <t>本体12DI/8DO＋本模块后达20DI/16DO，覆盖单元所需20DI/9DO（v9新增3个就地按钮后DI总点数由17增至20），EM DT16 或 EM DR16（8DI+8DO）</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>8</v>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -729,7 +733,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>每台PLC配1块，共8块；DI点数已用满、无冗余，如需预留余量可改选EM DE16等更大规格纯输入模块</t>
+          <t>每台PLC配1块，共8块；DI点数已用满、无冗余，如需预留余量可改选EM DE16等更大规格纯输入模块；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -758,7 +762,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>现场1台集中管理8套缸单元，用于总览/报警详情/报警确认/参数设定/历史记录/手动调试；优先昆仑通态MCGS、威纶通、步科、显控等，需向厂家确认8站点同时通讯能力、变量点数、报警/历史记录容量</t>
+          <t>现场1台集中管理8套缸单元，用于总览/报警详情/报警确认/参数设定/历史记录/手动调试；优先昆仑通态MCGS、威纶通、步科、显控等，需向厂家确认8站点同时通讯能力、变量点数、报警/历史记录容量；首期即采购1台，按8套满配选型（变量点数/连接数/容量），避免扩展时更换硬件</t>
         </is>
       </c>
     </row>
@@ -787,7 +791,7 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>优先选用随屏免费提供的组态软件（如昆仑通态MCGS嵌入版）；需确认S7-200 SMART以太网驱动支持方式、8站点授权、变量点数及报警/历史记录容量是否满足</t>
+          <t>优先选用随屏免费提供的组态软件（如昆仑通态MCGS嵌入版）；需确认S7-200 SMART以太网驱动支持方式、8站点授权、变量点数及报警/历史记录容量是否满足；首期即采购1套，授权按8套满配核算</t>
         </is>
       </c>
     </row>
@@ -816,7 +820,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>已确认8套缸同处一个实验室、彼此距离不远，1台即可，无需分级级联或光纤转换</t>
+          <t>已确认8套缸同处一个实验室、彼此距离不远，1台即可，无需分级级联或光纤转换；首期即采购1台，必须选9口及以上（按8台PLC+1台HMI满配选型），避免扩展时更换</t>
         </is>
       </c>
     </row>
@@ -845,7 +849,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>随现场布线距离核算用量</t>
+          <t>随现场布线距离核算用量；首期按1套布线核算用量，扩展时追加；建议首期即按8套规划线槽和主干布线</t>
         </is>
       </c>
     </row>
@@ -864,8 +868,10 @@
           <t>消音按钮＋报警确认/复位按钮＋系统复位按钮（急停解除专用，与报警确认按钮物理分离）＋对应状态指示灯，不含触摸屏</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>8</v>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -874,7 +880,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>每套缸单元1套，替代原就地触摸屏方案；急停按钮单独见本表第18项</t>
+          <t>每套缸单元1套，替代原就地触摸屏方案；急停按钮单独见本表第18项；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -893,8 +899,10 @@
           <t>为PLC、传感器、继电器线圈供电，容量待核算</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>8</v>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -903,7 +911,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>每套缸单元1台，容量需按全负载核算后选型；若最终采用集中大柜方案可能合并配电，待控制柜方案确定后调整</t>
+          <t>每套缸单元1台，容量需按全负载核算后选型；若最终采用集中大柜方案可能合并配电，待控制柜方案确定后调整；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -926,8 +934,10 @@
           <t>得电打开/失电关闭失效安全型，1/4-28或对应管径接口</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>16</v>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量16</t>
+        </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -936,7 +946,7 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>每套缸2个（上缸、下缸各1个，独立第二道漫溢保护），共8套16个</t>
+          <t>每套缸2个（上缸、下缸各1个，独立第二道漫溢保护），共8套16个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -955,8 +965,10 @@
           <t>自带开到位/关到位限位反馈信号（有源正极输出）</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>24</v>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量24</t>
+        </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -965,7 +977,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>每套缸对应阀A/B/C共3个，共8套24个，勒隆阀门或同等产品</t>
+          <t>每套缸对应阀A/B/C共3个，共8套24个，勒隆阀门或同等产品；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -988,8 +1000,10 @@
           <t>开关量输出，无源触点</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>40</v>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量40</t>
+        </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -998,7 +1012,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>每套缸5个（阀A/B/C各1个＋潜水泵1/2各1个），共8套40个</t>
+          <t>每套缸5个（阀A/B/C各1个＋潜水泵1/2各1个），共8套40个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1017,8 +1031,10 @@
           <t>同时具备最高/最低两个判定点，无源触点输出</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>16</v>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量16</t>
+        </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1027,7 +1043,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>每套缸2个（对应上缸A、下缸B），共8套16个</t>
+          <t>每套缸2个（对应上缸A、下缸B），共8套16个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1046,8 +1062,10 @@
           <t>Modbus RTU 485通讯，量程按上缸进水流量选型</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>8</v>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1056,7 +1074,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，共8个，已确认协议，型号K24或同等产品</t>
+          <t>每套缸1个，共8个，已确认协议，型号K24或同等产品；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1079,8 +1097,10 @@
           <t>上缸搅拌用，串接流量开关做运行反馈</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>16</v>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量16</t>
+        </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1089,7 +1109,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>每套缸2台，共8套16台</t>
+          <t>每套缸2台，共8套16台；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1108,8 +1128,10 @@
           <t>柱塞式计量泵，Modbus RTU 485通讯，含内部切换阀</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>8</v>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1118,7 +1140,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>每套缸1台，共8台，已确认Modbus协议，配套进样器规格按加药量核实</t>
+          <t>每套缸1台，共8台，已确认Modbus协议，配套进样器规格按加药量核实；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1141,8 +1163,10 @@
           <t>工业级，至少2组独立常闭触点（1组接安全继电器，1组接PLC监测）</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>8</v>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1151,7 +1175,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，各自独立，不设总控室级联动急停</t>
+          <t>每套缸1个，各自独立，不设总控室级联动急停；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1170,8 +1194,10 @@
           <t>强制导向型（force-guided），建议符合EN ISO 13849-1/IEC 60204-1标准</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>8</v>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1180,7 +1206,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，切断该套单元潜水泵/注射泵/电动球阀动力回路</t>
+          <t>每套缸1个，切断该套单元潜水泵/注射泵/电动球阀动力回路；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1203,8 +1229,10 @@
           <t>PLC数字量输出统一经继电器转换驱动负载，24V DC线圈</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>72</v>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量72</t>
+        </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1213,7 +1241,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>每套缸9个（对应9个DO点：潜水泵×2、电动球阀×3、NC电磁阀×2、声/光报警×2），共8套72个</t>
+          <t>每套缸9个（对应9个DO点：潜水泵×2、电动球阀×3、NC电磁阀×2、声/光报警×2），共8套72个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1232,8 +1260,10 @@
           <t>阀门限位反馈为有源正极输出，需转换为无源触点接入PLC</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>48</v>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量48</t>
+        </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1242,7 +1272,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>每套缸6个（阀A/B/C各自开到位/关到位共6路），共8套48个</t>
+          <t>每套缸6个（阀A/B/C各自开到位/关到位共6路），共8套48个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1261,8 +1291,10 @@
           <t>标准DIN导轨安装，含接线端子、线槽、标签</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>8</v>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1271,7 +1303,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>每套缸单元1批，共8批；若控制柜改为集中大柜方案可合并核算用量</t>
+          <t>每套缸单元1批，共8批；若控制柜改为集中大柜方案可合并核算用量；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1290,8 +1322,10 @@
           <t>屏蔽双绞线，每套单元1条独立总线，连接本单元PLC与2个485从站（注射泵/流量计）</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>8</v>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1300,7 +1334,7 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>每套缸独立1批总线，共8批，不与其他单元共享总线</t>
+          <t>每套缸独立1批总线，共8批，不与其他单元共享总线；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1319,8 +1353,10 @@
           <t>120Ω，每条总线两端各接1个</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>16</v>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量16</t>
+        </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1329,7 +1365,7 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>每套缸2个，共8套16个</t>
+          <t>每套缸2个，共8套16个；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1352,8 +1388,10 @@
           <t>无源触点驱动，独立消音控制</t>
         </is>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>8</v>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1362,7 +1400,7 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，各自独立，不设总控室汇总报警</t>
+          <t>每套缸1个，各自独立，不设总控室汇总报警；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1381,8 +1419,10 @@
           <t>无源触点驱动，独立消光控制（需就地面板按钮人工确认复位）</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>8</v>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1391,7 +1431,7 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>每套缸1个，各自独立</t>
+          <t>每套缸1个，各自独立；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
@@ -1414,8 +1454,10 @@
           <t>含PLC、继电器、端子排等全部电气元件安装空间</t>
         </is>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>8</v>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>首期1 / 全量8</t>
+        </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1424,12 +1466,11 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>布置方案（8套独立小柜就近安装 / 1个大柜内隔8个分区）待现场勘察玻璃缸实际摆放布局后确定；此处暂按独立小柜方案列8台，若改集中大柜需合并调整</t>
+          <t>布置方案（8套独立小柜就近安装 / 1个大柜内隔8个分区）待现场勘察玻璃缸实际摆放布局后确定；此处暂按独立小柜方案列8台，若改集中大柜需合并调整；【v9.3分期】首期1套，后续按需扩展至全量8套，扩展时按套追加</t>
         </is>
       </c>
     </row>
     <row r="30" ht="372" customHeight="1" s="13"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="6" t="n"/>
     </row>
